--- a/docs/assets/coremeta4cat_vocabulary.xlsx
+++ b/docs/assets/coremeta4cat_vocabulary.xlsx
@@ -12141,7 +12141,7 @@
       <c r="H261" s="13" t="inlineStr"/>
       <c r="I261" s="13" t="inlineStr">
         <is>
-          <t>SIO:000008</t>
+          <t>voc4cat:0008114</t>
         </is>
       </c>
       <c r="J261" s="13" t="inlineStr">
